--- a/StructureDefinition-mii-pr-icu-beatmung.xlsx
+++ b/StructureDefinition-mii-pr-icu-beatmung.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$144</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5106" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5067" uniqueCount="653">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T06:46:19+00:00</t>
+    <t>2026-09-15T22:20:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1281,9 +1281,6 @@
   </si>
   <si>
     <t>Procedure.code.coding.extension.value[x].code</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Procedure.code.coding:ops.extension:Seitenlokalisation.value[x].display</t>
@@ -1810,22 +1807,6 @@
   </si>
   <si>
     <t>Procedure.bodySite.extension</t>
-  </si>
-  <si>
-    <t>Procedure.bodySite.extension:bodySite</t>
-  </si>
-  <si>
-    <t>bodySite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {bodySite}
-</t>
-  </si>
-  <si>
-    <t>Target anatomic location or structure</t>
-  </si>
-  <si>
-    <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
   </si>
   <si>
     <t>Procedure.bodySite.coding</t>
@@ -2380,7 +2361,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM145"/>
+  <dimension ref="A1:AM144"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.5703125" customWidth="true" bestFit="true"/>
@@ -4624,7 +4605,7 @@
         <v>77</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>112</v>
@@ -4844,7 +4825,7 @@
         <v>84</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>96</v>
@@ -9278,7 +9259,7 @@
         <v>77</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>112</v>
@@ -9609,7 +9590,7 @@
         <v>77</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>112</v>
@@ -9827,7 +9808,7 @@
         <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>96</v>
@@ -10047,7 +10028,7 @@
         <v>77</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>112</v>
@@ -10160,7 +10141,7 @@
         <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>96</v>
@@ -10271,7 +10252,7 @@
         <v>84</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>96</v>
@@ -10322,9 +10303,7 @@
       <c r="M72" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="N72" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
         <v>243</v>
       </c>
@@ -10384,7 +10363,7 @@
         <v>84</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>96</v>
@@ -10401,10 +10380,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B73" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10435,9 +10414,7 @@
       <c r="M73" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="N73" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
         <v>250</v>
       </c>
@@ -10497,7 +10474,7 @@
         <v>84</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>96</v>
@@ -10514,10 +10491,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B74" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10610,7 +10587,7 @@
         <v>84</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>96</v>
@@ -10627,10 +10604,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B75" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10656,7 +10633,7 @@
         <v>125</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M75" t="s" s="2">
         <v>226</v>
@@ -10672,7 +10649,7 @@
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>75</v>
@@ -10723,7 +10700,7 @@
         <v>84</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>96</v>
@@ -10740,10 +10717,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B76" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10769,10 +10746,10 @@
         <v>98</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>236</v>
@@ -10834,7 +10811,7 @@
         <v>84</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>96</v>
@@ -10851,10 +10828,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10880,14 +10857,12 @@
         <v>159</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="M77" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="N77" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
         <v>243</v>
       </c>
@@ -10902,7 +10877,7 @@
         <v>75</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>75</v>
@@ -10947,10 +10922,10 @@
         <v>84</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>75</v>
@@ -10964,10 +10939,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="B78" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10998,9 +10973,7 @@
       <c r="M78" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="N78" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
         <v>250</v>
       </c>
@@ -11060,7 +11033,7 @@
         <v>84</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>96</v>
@@ -11077,10 +11050,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B79" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11173,7 +11146,7 @@
         <v>84</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>96</v>
@@ -11190,7 +11163,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>370</v>
@@ -11259,7 +11232,7 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>75</v>
@@ -11303,7 +11276,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>379</v>
@@ -11412,7 +11385,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>381</v>
@@ -11523,10 +11496,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11636,10 +11609,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11747,10 +11720,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11858,10 +11831,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11969,10 +11942,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12082,10 +12055,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12195,14 +12168,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12221,13 +12194,13 @@
         <v>85</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12278,7 +12251,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>84</v>
@@ -12293,21 +12266,21 @@
         <v>96</v>
       </c>
       <c r="AK89" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AL89" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AL89" t="s" s="2">
+      <c r="AM89" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>446</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12413,10 +12386,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12524,10 +12497,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12553,13 +12526,13 @@
         <v>98</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12609,16 +12582,16 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI92" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>96</v>
@@ -12635,10 +12608,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12664,13 +12637,13 @@
         <v>125</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12699,28 +12672,28 @@
         <v>141</v>
       </c>
       <c r="Y93" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="Z93" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="Z93" t="s" s="2">
+      <c r="AA93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -12746,10 +12719,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12775,13 +12748,13 @@
         <v>268</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -12831,7 +12804,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -12857,10 +12830,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12886,13 +12859,13 @@
         <v>98</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -12942,7 +12915,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -12968,10 +12941,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12994,16 +12967,16 @@
         <v>85</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13053,7 +13026,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -13068,21 +13041,21 @@
         <v>96</v>
       </c>
       <c r="AK96" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AL96" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="AL96" t="s" s="2">
+      <c r="AM96" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>479</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13188,10 +13161,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13299,10 +13272,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13328,13 +13301,13 @@
         <v>98</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13384,16 +13357,16 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI99" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>96</v>
@@ -13410,10 +13383,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13439,13 +13412,13 @@
         <v>125</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13474,28 +13447,28 @@
         <v>141</v>
       </c>
       <c r="Y100" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="Z100" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="Z100" t="s" s="2">
+      <c r="AA100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -13521,10 +13494,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13550,13 +13523,13 @@
         <v>268</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13606,7 +13579,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
@@ -13632,10 +13605,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13661,13 +13634,13 @@
         <v>98</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13717,7 +13690,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
@@ -13743,10 +13716,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13769,16 +13742,16 @@
         <v>85</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -13816,17 +13789,17 @@
         <v>75</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
@@ -13841,24 +13814,24 @@
         <v>96</v>
       </c>
       <c r="AK103" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AL103" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="AL103" t="s" s="2">
+      <c r="AM103" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>495</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C104" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="C104" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>75</v>
@@ -13883,13 +13856,13 @@
         <v>203</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M104" t="s" s="2">
-        <v>499</v>
-      </c>
       <c r="N104" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -13939,7 +13912,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
@@ -13954,24 +13927,24 @@
         <v>96</v>
       </c>
       <c r="AK104" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AL104" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="AL104" t="s" s="2">
+      <c r="AM104" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>495</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C105" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="C105" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>75</v>
@@ -13993,16 +13966,16 @@
         <v>85</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="M105" t="s" s="2">
-        <v>503</v>
-      </c>
       <c r="N105" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14052,7 +14025,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -14067,21 +14040,21 @@
         <v>96</v>
       </c>
       <c r="AK105" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AL105" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="AL105" t="s" s="2">
+      <c r="AM105" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>495</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14104,13 +14077,13 @@
         <v>85</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="L106" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="L106" t="s" s="2">
+      <c r="M106" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14161,7 +14134,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -14179,7 +14152,7 @@
         <v>75</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>75</v>
@@ -14187,10 +14160,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14213,13 +14186,13 @@
         <v>85</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14270,7 +14243,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -14288,7 +14261,7 @@
         <v>75</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>75</v>
@@ -14296,10 +14269,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14322,13 +14295,13 @@
         <v>85</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="L108" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="L108" t="s" s="2">
+      <c r="M108" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14379,7 +14352,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>76</v>
@@ -14394,7 +14367,7 @@
         <v>96</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AL108" t="s" s="2">
         <v>75</v>
@@ -14405,10 +14378,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14514,10 +14487,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14625,14 +14598,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -14654,10 +14627,10 @@
         <v>104</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="N111" t="s" s="2">
         <v>107</v>
@@ -14712,7 +14685,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -14738,10 +14711,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14767,14 +14740,14 @@
         <v>308</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>75</v>
@@ -14802,11 +14775,11 @@
         <v>149</v>
       </c>
       <c r="Y112" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="Z112" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="Z112" t="s" s="2">
-        <v>531</v>
-      </c>
       <c r="AA112" t="s" s="2">
         <v>75</v>
       </c>
@@ -14823,7 +14796,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -14838,21 +14811,21 @@
         <v>96</v>
       </c>
       <c r="AK112" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM112" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>533</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14875,17 +14848,17 @@
         <v>85</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="L113" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="M113" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>75</v>
@@ -14934,7 +14907,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>84</v>
@@ -14949,21 +14922,21 @@
         <v>96</v>
       </c>
       <c r="AK113" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AL113" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="AL113" t="s" s="2">
+      <c r="AM113" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>541</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14986,17 +14959,17 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="L114" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="L114" t="s" s="2">
+      <c r="M114" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>75</v>
@@ -15045,7 +15018,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -15071,10 +15044,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15097,17 +15070,17 @@
         <v>85</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="L115" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="L115" t="s" s="2">
+      <c r="M115" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>75</v>
@@ -15156,7 +15129,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -15174,7 +15147,7 @@
         <v>75</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>75</v>
@@ -15182,10 +15155,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15211,13 +15184,13 @@
         <v>308</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="N116" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -15246,11 +15219,11 @@
         <v>149</v>
       </c>
       <c r="Y116" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="Z116" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="Z116" t="s" s="2">
-        <v>558</v>
-      </c>
       <c r="AA116" t="s" s="2">
         <v>75</v>
       </c>
@@ -15267,7 +15240,7 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>76</v>
@@ -15282,10 +15255,10 @@
         <v>96</v>
       </c>
       <c r="AK116" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AL116" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>75</v>
@@ -15293,10 +15266,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15319,16 +15292,16 @@
         <v>85</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="L117" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="L117" t="s" s="2">
+      <c r="M117" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="M117" t="s" s="2">
+      <c r="N117" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15378,7 +15351,7 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>76</v>
@@ -15393,10 +15366,10 @@
         <v>96</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>75</v>
@@ -15404,10 +15377,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15433,13 +15406,13 @@
         <v>308</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="M118" t="s" s="2">
+      <c r="N118" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15468,11 +15441,11 @@
         <v>149</v>
       </c>
       <c r="Y118" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="Z118" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="Z118" t="s" s="2">
-        <v>572</v>
-      </c>
       <c r="AA118" t="s" s="2">
         <v>75</v>
       </c>
@@ -15489,7 +15462,7 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
@@ -15510,15 +15483,15 @@
         <v>75</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15624,10 +15597,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15735,14 +15708,12 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="C121" t="s" s="2">
-        <v>577</v>
-      </c>
+      <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
         <v>75</v>
       </c>
@@ -15751,28 +15722,32 @@
         <v>76</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>578</v>
+        <v>137</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>579</v>
+        <v>324</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P121" t="s" s="2">
         <v>75</v>
       </c>
@@ -15808,19 +15783,17 @@
         <v>75</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="AC121" s="2"/>
       <c r="AD121" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>111</v>
+        <v>329</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>76</v>
@@ -15832,7 +15805,7 @@
         <v>75</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>75</v>
@@ -15841,17 +15814,19 @@
         <v>75</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>75</v>
+        <v>330</v>
       </c>
     </row>
-    <row r="122" hidden="true">
+    <row r="122">
       <c r="A122" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="C122" s="2"/>
+        <v>575</v>
+      </c>
+      <c r="C122" t="s" s="2">
+        <v>578</v>
+      </c>
       <c r="D122" t="s" s="2">
         <v>75</v>
       </c>
@@ -15860,7 +15835,7 @@
         <v>76</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>85</v>
@@ -15875,10 +15850,10 @@
         <v>137</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="N122" t="s" s="2">
         <v>326</v>
@@ -15921,14 +15896,16 @@
         <v>75</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AC122" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD122" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE122" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF122" t="s" s="2">
         <v>329</v>
@@ -15955,16 +15932,14 @@
         <v>330</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="C123" t="s" s="2">
-        <v>584</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
         <v>75</v>
       </c>
@@ -15976,29 +15951,25 @@
         <v>84</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>333</v>
+        <v>99</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N123" s="2"/>
+      <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>75</v>
       </c>
@@ -16046,19 +16017,19 @@
         <v>75</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>329</v>
+        <v>101</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>75</v>
@@ -16067,26 +16038,26 @@
         <v>75</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>330</v>
+        <v>75</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>75</v>
@@ -16098,15 +16069,17 @@
         <v>75</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N124" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>75</v>
@@ -16143,31 +16116,31 @@
         <v>75</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="AC124" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AD124" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>75</v>
@@ -16179,46 +16152,48 @@
         <v>75</v>
       </c>
     </row>
-    <row r="125" hidden="true">
+    <row r="125">
       <c r="A125" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>105</v>
+        <v>225</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>106</v>
+        <v>226</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O125" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P125" t="s" s="2">
         <v>75</v>
       </c>
@@ -16227,7 +16202,7 @@
         <v>75</v>
       </c>
       <c r="S125" t="s" s="2">
-        <v>75</v>
+        <v>229</v>
       </c>
       <c r="T125" t="s" s="2">
         <v>75</v>
@@ -16254,31 +16229,31 @@
         <v>75</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC125" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD125" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>111</v>
+        <v>230</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>75</v>
@@ -16287,15 +16262,15 @@
         <v>75</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16303,7 +16278,7 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G126" t="s" s="2">
         <v>84</v>
@@ -16318,20 +16293,18 @@
         <v>85</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
         <v>75</v>
       </c>
@@ -16340,7 +16313,7 @@
         <v>75</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>229</v>
+        <v>75</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>75</v>
@@ -16379,7 +16352,7 @@
         <v>75</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>76</v>
@@ -16400,15 +16373,15 @@
         <v>75</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16416,7 +16389,7 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>84</v>
@@ -16431,18 +16404,18 @@
         <v>85</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O127" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="P127" t="s" s="2">
         <v>75</v>
       </c>
@@ -16490,7 +16463,7 @@
         <v>75</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>76</v>
@@ -16511,15 +16484,15 @@
         <v>75</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16527,13 +16500,13 @@
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G128" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>75</v>
@@ -16542,17 +16515,17 @@
         <v>85</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>75</v>
@@ -16601,7 +16574,7 @@
         <v>75</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>76</v>
@@ -16622,15 +16595,15 @@
         <v>75</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16653,17 +16626,19 @@
         <v>85</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>98</v>
+        <v>255</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N129" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O129" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>75</v>
@@ -16712,7 +16687,7 @@
         <v>75</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>76</v>
@@ -16733,15 +16708,15 @@
         <v>75</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>252</v>
+        <v>261</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16764,19 +16739,19 @@
         <v>85</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>255</v>
+        <v>98</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>256</v>
+        <v>352</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>257</v>
+        <v>353</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>258</v>
+        <v>354</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>259</v>
+        <v>355</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>75</v>
@@ -16825,7 +16800,7 @@
         <v>75</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>260</v>
+        <v>356</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>76</v>
@@ -16846,15 +16821,15 @@
         <v>75</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>261</v>
+        <v>357</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16877,20 +16852,18 @@
         <v>85</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>98</v>
+        <v>308</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>352</v>
+        <v>595</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>353</v>
+        <v>596</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>597</v>
+      </c>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>75</v>
       </c>
@@ -16914,13 +16887,13 @@
         <v>75</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>75</v>
+        <v>598</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>75</v>
+        <v>599</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>75</v>
@@ -16938,7 +16911,7 @@
         <v>75</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>356</v>
+        <v>594</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
@@ -16959,7 +16932,7 @@
         <v>75</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>357</v>
+        <v>75</v>
       </c>
     </row>
     <row r="132" hidden="true">
@@ -16978,7 +16951,7 @@
         <v>76</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>75</v>
@@ -16987,19 +16960,19 @@
         <v>75</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>308</v>
+        <v>601</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -17025,13 +16998,13 @@
         <v>75</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>604</v>
+        <v>75</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>605</v>
+        <v>75</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>75</v>
@@ -17055,7 +17028,7 @@
         <v>76</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>75</v>
@@ -17075,10 +17048,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17101,16 +17074,16 @@
         <v>75</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="L133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -17136,13 +17109,13 @@
         <v>75</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>75</v>
+        <v>609</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>75</v>
+        <v>610</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>75</v>
@@ -17160,7 +17133,7 @@
         <v>75</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>76</v>
@@ -17212,18 +17185,18 @@
         <v>75</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>308</v>
+        <v>612</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="N134" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="O134" s="2"/>
+      <c r="N134" s="2"/>
+      <c r="O134" t="s" s="2">
+        <v>615</v>
+      </c>
       <c r="P134" t="s" s="2">
         <v>75</v>
       </c>
@@ -17247,13 +17220,13 @@
         <v>75</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>615</v>
+        <v>75</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>616</v>
+        <v>75</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>75</v>
@@ -17297,10 +17270,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17323,18 +17296,16 @@
         <v>75</v>
       </c>
       <c r="K135" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="L135" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>620</v>
-      </c>
       <c r="N135" s="2"/>
-      <c r="O135" t="s" s="2">
-        <v>621</v>
-      </c>
+      <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>75</v>
       </c>
@@ -17358,13 +17329,13 @@
         <v>75</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>75</v>
+        <v>619</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>75</v>
+        <v>620</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>75</v>
@@ -17382,7 +17353,7 @@
         <v>75</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>76</v>
@@ -17406,12 +17377,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="136" hidden="true">
+    <row r="136">
       <c r="A136" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17425,7 +17396,7 @@
         <v>77</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>75</v>
@@ -17434,7 +17405,7 @@
         <v>75</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>308</v>
+        <v>622</v>
       </c>
       <c r="L136" t="s" s="2">
         <v>623</v>
@@ -17467,13 +17438,13 @@
         <v>75</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>625</v>
+        <v>75</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>626</v>
+        <v>75</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>75</v>
@@ -17491,7 +17462,7 @@
         <v>75</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>76</v>
@@ -17506,16 +17477,16 @@
         <v>96</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>75</v>
+        <v>625</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>75</v>
+        <v>626</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
         <v>627</v>
       </c>
@@ -17534,7 +17505,7 @@
         <v>77</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>75</v>
@@ -17543,13 +17514,13 @@
         <v>75</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="L137" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="L137" t="s" s="2">
+      <c r="M137" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -17615,21 +17586,21 @@
         <v>96</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>631</v>
+        <v>75</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>632</v>
+        <v>75</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17640,7 +17611,7 @@
         <v>76</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>75</v>
@@ -17652,13 +17623,13 @@
         <v>75</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>515</v>
+        <v>98</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>634</v>
+        <v>99</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>635</v>
+        <v>100</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -17709,19 +17680,19 @@
         <v>75</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>633</v>
+        <v>101</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>75</v>
@@ -17735,21 +17706,21 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>75</v>
@@ -17761,15 +17732,17 @@
         <v>75</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N139" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>75</v>
@@ -17818,19 +17791,19 @@
         <v>75</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>75</v>
@@ -17844,14 +17817,14 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>103</v>
+        <v>521</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -17864,24 +17837,26 @@
         <v>75</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K140" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>105</v>
+        <v>522</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>106</v>
+        <v>523</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="O140" s="2"/>
+      <c r="O140" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P140" t="s" s="2">
         <v>75</v>
       </c>
@@ -17929,7 +17904,7 @@
         <v>75</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>111</v>
+        <v>524</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>76</v>
@@ -17955,46 +17930,42 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>522</v>
+        <v>75</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I141" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>104</v>
+        <v>308</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>523</v>
+        <v>634</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>635</v>
+      </c>
+      <c r="N141" s="2"/>
+      <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>75</v>
       </c>
@@ -18018,13 +17989,13 @@
         <v>75</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>75</v>
+        <v>636</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>75</v>
+        <v>637</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>75</v>
@@ -18042,19 +18013,19 @@
         <v>75</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>525</v>
+        <v>633</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>75</v>
@@ -18068,10 +18039,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18079,7 +18050,7 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G142" t="s" s="2">
         <v>84</v>
@@ -18094,7 +18065,7 @@
         <v>75</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>308</v>
+        <v>639</v>
       </c>
       <c r="L142" t="s" s="2">
         <v>640</v>
@@ -18127,13 +18098,13 @@
         <v>75</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>163</v>
+        <v>75</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>642</v>
+        <v>75</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>643</v>
+        <v>75</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>75</v>
@@ -18151,10 +18122,10 @@
         <v>75</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>84</v>
@@ -18177,10 +18148,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18188,10 +18159,10 @@
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>75</v>
@@ -18203,16 +18174,20 @@
         <v>75</v>
       </c>
       <c r="K143" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="L143" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="L143" t="s" s="2">
+      <c r="N143" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="M143" t="s" s="2">
+      <c r="O143" t="s" s="2">
         <v>647</v>
       </c>
-      <c r="N143" s="2"/>
-      <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>75</v>
       </c>
@@ -18260,13 +18235,13 @@
         <v>75</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>75</v>
@@ -18312,20 +18287,18 @@
         <v>75</v>
       </c>
       <c r="K144" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L144" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="L144" t="s" s="2">
+      <c r="M144" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="M144" t="s" s="2">
-        <v>651</v>
-      </c>
       <c r="N144" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="O144" t="s" s="2">
-        <v>653</v>
-      </c>
+        <v>646</v>
+      </c>
+      <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
         <v>75</v>
       </c>
@@ -18349,13 +18322,13 @@
         <v>75</v>
       </c>
       <c r="X144" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="Y144" t="s" s="2">
-        <v>75</v>
+        <v>651</v>
       </c>
       <c r="Z144" t="s" s="2">
-        <v>75</v>
+        <v>652</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>75</v>
@@ -18397,119 +18370,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="145" hidden="true">
-      <c r="A145" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="B145" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="C145" s="2"/>
-      <c r="D145" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E145" s="2"/>
-      <c r="F145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G145" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H145" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I145" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J145" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K145" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="L145" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="N145" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="O145" s="2"/>
-      <c r="P145" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q145" s="2"/>
-      <c r="R145" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S145" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T145" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U145" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V145" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W145" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X145" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="Y145" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="Z145" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="AA145" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB145" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC145" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD145" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE145" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF145" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="AG145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH145" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI145" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ145" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK145" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL145" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM145" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AM145">
+  <autoFilter ref="A1:AM144">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18519,7 +18381,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI144">
+  <conditionalFormatting sqref="A2:AI143">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-mii-pr-icu-beatmung.xlsx
+++ b/StructureDefinition-mii-pr-icu-beatmung.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$145</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5067" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5106" uniqueCount="659">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T22:20:02+00:00</t>
+    <t>2026-09-17T12:17:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1281,6 +1281,9 @@
   </si>
   <si>
     <t>Procedure.code.coding.extension.value[x].code</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Procedure.code.coding:ops.extension:Seitenlokalisation.value[x].display</t>
@@ -1807,6 +1810,22 @@
   </si>
   <si>
     <t>Procedure.bodySite.extension</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension:bodySite</t>
+  </si>
+  <si>
+    <t>bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {bodySite}
+</t>
+  </si>
+  <si>
+    <t>Target anatomic location or structure</t>
+  </si>
+  <si>
+    <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
   </si>
   <si>
     <t>Procedure.bodySite.coding</t>
@@ -2361,7 +2380,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM144"/>
+  <dimension ref="A1:AM145"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.5703125" customWidth="true" bestFit="true"/>
@@ -4605,7 +4624,7 @@
         <v>77</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>112</v>
@@ -4825,7 +4844,7 @@
         <v>84</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>96</v>
@@ -9259,7 +9278,7 @@
         <v>77</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>112</v>
@@ -9590,7 +9609,7 @@
         <v>77</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>112</v>
@@ -9808,7 +9827,7 @@
         <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>96</v>
@@ -10028,7 +10047,7 @@
         <v>77</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>112</v>
@@ -10141,7 +10160,7 @@
         <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>96</v>
@@ -10252,7 +10271,7 @@
         <v>84</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>96</v>
@@ -10303,7 +10322,9 @@
       <c r="M72" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="N72" s="2"/>
+      <c r="N72" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O72" t="s" s="2">
         <v>243</v>
       </c>
@@ -10363,7 +10384,7 @@
         <v>84</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>96</v>
@@ -10380,10 +10401,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10414,7 +10435,9 @@
       <c r="M73" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="N73" s="2"/>
+      <c r="N73" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O73" t="s" s="2">
         <v>250</v>
       </c>
@@ -10474,7 +10497,7 @@
         <v>84</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>96</v>
@@ -10491,10 +10514,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10587,7 +10610,7 @@
         <v>84</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>96</v>
@@ -10604,10 +10627,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10633,7 +10656,7 @@
         <v>125</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M75" t="s" s="2">
         <v>226</v>
@@ -10649,7 +10672,7 @@
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>75</v>
@@ -10700,7 +10723,7 @@
         <v>84</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>96</v>
@@ -10717,10 +10740,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10746,10 +10769,10 @@
         <v>98</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>236</v>
@@ -10811,7 +10834,7 @@
         <v>84</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>96</v>
@@ -10828,10 +10851,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10857,12 +10880,14 @@
         <v>159</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M77" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="N77" s="2"/>
+      <c r="N77" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O77" t="s" s="2">
         <v>243</v>
       </c>
@@ -10877,7 +10902,7 @@
         <v>75</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>75</v>
@@ -10922,10 +10947,10 @@
         <v>84</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>75</v>
@@ -10939,10 +10964,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10973,7 +10998,9 @@
       <c r="M78" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="N78" s="2"/>
+      <c r="N78" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O78" t="s" s="2">
         <v>250</v>
       </c>
@@ -11033,7 +11060,7 @@
         <v>84</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>96</v>
@@ -11050,10 +11077,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11146,7 +11173,7 @@
         <v>84</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>96</v>
@@ -11163,7 +11190,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>370</v>
@@ -11232,7 +11259,7 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>75</v>
@@ -11276,7 +11303,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>379</v>
@@ -11385,7 +11412,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>381</v>
@@ -11496,10 +11523,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11609,10 +11636,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11720,10 +11747,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11831,10 +11858,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11942,10 +11969,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12055,10 +12082,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12168,14 +12195,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12194,13 +12221,13 @@
         <v>85</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12251,7 +12278,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>84</v>
@@ -12266,21 +12293,21 @@
         <v>96</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12386,10 +12413,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12497,10 +12524,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12526,13 +12553,13 @@
         <v>98</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12582,7 +12609,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -12591,7 +12618,7 @@
         <v>84</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>96</v>
@@ -12608,10 +12635,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12637,13 +12664,13 @@
         <v>125</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12672,10 +12699,10 @@
         <v>141</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>75</v>
@@ -12693,7 +12720,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -12719,10 +12746,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12748,13 +12775,13 @@
         <v>268</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -12804,7 +12831,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -12830,10 +12857,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12859,13 +12886,13 @@
         <v>98</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -12915,7 +12942,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -12941,10 +12968,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12967,16 +12994,16 @@
         <v>85</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13026,7 +13053,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -13041,21 +13068,21 @@
         <v>96</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13161,10 +13188,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13272,10 +13299,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13301,13 +13328,13 @@
         <v>98</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13357,7 +13384,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -13366,7 +13393,7 @@
         <v>84</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>96</v>
@@ -13383,10 +13410,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13412,13 +13439,13 @@
         <v>125</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13447,10 +13474,10 @@
         <v>141</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>75</v>
@@ -13468,7 +13495,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -13494,10 +13521,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13523,13 +13550,13 @@
         <v>268</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13579,7 +13606,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
@@ -13605,10 +13632,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13634,13 +13661,13 @@
         <v>98</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13690,7 +13717,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
@@ -13716,10 +13743,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13742,16 +13769,16 @@
         <v>85</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -13789,17 +13816,17 @@
         <v>75</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
@@ -13814,24 +13841,24 @@
         <v>96</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>75</v>
@@ -13856,13 +13883,13 @@
         <v>203</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -13912,7 +13939,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
@@ -13927,24 +13954,24 @@
         <v>96</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>75</v>
@@ -13966,16 +13993,16 @@
         <v>85</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14025,7 +14052,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -14040,21 +14067,21 @@
         <v>96</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14077,13 +14104,13 @@
         <v>85</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14134,7 +14161,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -14152,7 +14179,7 @@
         <v>75</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>75</v>
@@ -14160,10 +14187,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14186,13 +14213,13 @@
         <v>85</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14243,7 +14270,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -14261,7 +14288,7 @@
         <v>75</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>75</v>
@@ -14269,10 +14296,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14295,13 +14322,13 @@
         <v>85</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14352,7 +14379,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>76</v>
@@ -14367,7 +14394,7 @@
         <v>96</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AL108" t="s" s="2">
         <v>75</v>
@@ -14378,10 +14405,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14487,10 +14514,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14598,14 +14625,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -14627,10 +14654,10 @@
         <v>104</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N111" t="s" s="2">
         <v>107</v>
@@ -14685,7 +14712,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -14711,10 +14738,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14740,14 +14767,14 @@
         <v>308</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>75</v>
@@ -14775,10 +14802,10 @@
         <v>149</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>75</v>
@@ -14796,7 +14823,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -14811,21 +14838,21 @@
         <v>96</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14848,17 +14875,17 @@
         <v>85</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>75</v>
@@ -14907,7 +14934,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>84</v>
@@ -14922,21 +14949,21 @@
         <v>96</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14959,17 +14986,17 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>75</v>
@@ -15018,7 +15045,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -15044,10 +15071,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15070,17 +15097,17 @@
         <v>85</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>75</v>
@@ -15129,7 +15156,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -15147,7 +15174,7 @@
         <v>75</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>75</v>
@@ -15155,10 +15182,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15184,13 +15211,13 @@
         <v>308</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -15219,10 +15246,10 @@
         <v>149</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>75</v>
@@ -15240,7 +15267,7 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>76</v>
@@ -15255,10 +15282,10 @@
         <v>96</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>75</v>
@@ -15266,10 +15293,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15292,16 +15319,16 @@
         <v>85</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15351,7 +15378,7 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>76</v>
@@ -15366,10 +15393,10 @@
         <v>96</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>75</v>
@@ -15377,10 +15404,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15406,13 +15433,13 @@
         <v>308</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15441,10 +15468,10 @@
         <v>149</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>75</v>
@@ -15462,7 +15489,7 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
@@ -15483,15 +15510,15 @@
         <v>75</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15597,10 +15624,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15708,12 +15735,14 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="C121" s="2"/>
+      <c r="C121" t="s" s="2">
+        <v>577</v>
+      </c>
       <c r="D121" t="s" s="2">
         <v>75</v>
       </c>
@@ -15722,32 +15751,28 @@
         <v>76</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>137</v>
+        <v>578</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>324</v>
+        <v>579</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="N121" s="2"/>
+      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>75</v>
       </c>
@@ -15783,17 +15808,19 @@
         <v>75</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AC121" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD121" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>329</v>
+        <v>111</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>76</v>
@@ -15805,7 +15832,7 @@
         <v>75</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>75</v>
@@ -15814,19 +15841,17 @@
         <v>75</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>330</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="C122" t="s" s="2">
-        <v>578</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
         <v>75</v>
       </c>
@@ -15835,7 +15860,7 @@
         <v>76</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>85</v>
@@ -15850,10 +15875,10 @@
         <v>137</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="N122" t="s" s="2">
         <v>326</v>
@@ -15896,16 +15921,14 @@
         <v>75</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>582</v>
+      </c>
+      <c r="AC122" s="2"/>
       <c r="AD122" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE122" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF122" t="s" s="2">
         <v>329</v>
@@ -15932,14 +15955,16 @@
         <v>330</v>
       </c>
     </row>
-    <row r="123" hidden="true">
+    <row r="123">
       <c r="A123" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="C123" s="2"/>
+        <v>581</v>
+      </c>
+      <c r="C123" t="s" s="2">
+        <v>584</v>
+      </c>
       <c r="D123" t="s" s="2">
         <v>75</v>
       </c>
@@ -15951,25 +15976,29 @@
         <v>84</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>99</v>
+        <v>333</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N123" s="2"/>
-      <c r="O123" s="2"/>
+        <v>334</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P123" t="s" s="2">
         <v>75</v>
       </c>
@@ -16017,19 +16046,19 @@
         <v>75</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>101</v>
+        <v>329</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>75</v>
@@ -16038,26 +16067,26 @@
         <v>75</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>75</v>
+        <v>330</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>75</v>
@@ -16069,17 +16098,15 @@
         <v>75</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>75</v>
@@ -16116,31 +16143,31 @@
         <v>75</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC124" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD124" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>75</v>
@@ -16152,48 +16179,46 @@
         <v>75</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>225</v>
+        <v>105</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>226</v>
+        <v>106</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>75</v>
       </c>
@@ -16202,7 +16227,7 @@
         <v>75</v>
       </c>
       <c r="S125" t="s" s="2">
-        <v>229</v>
+        <v>75</v>
       </c>
       <c r="T125" t="s" s="2">
         <v>75</v>
@@ -16229,31 +16254,31 @@
         <v>75</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="AC125" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AD125" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>230</v>
+        <v>111</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>75</v>
@@ -16262,15 +16287,15 @@
         <v>75</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16278,7 +16303,7 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G126" t="s" s="2">
         <v>84</v>
@@ -16293,18 +16318,20 @@
         <v>85</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O126" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>75</v>
       </c>
@@ -16313,7 +16340,7 @@
         <v>75</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>75</v>
+        <v>229</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>75</v>
@@ -16352,7 +16379,7 @@
         <v>75</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>76</v>
@@ -16373,15 +16400,15 @@
         <v>75</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16389,7 +16416,7 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>84</v>
@@ -16404,18 +16431,18 @@
         <v>85</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N127" s="2"/>
-      <c r="O127" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>75</v>
       </c>
@@ -16463,7 +16490,7 @@
         <v>75</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>76</v>
@@ -16484,15 +16511,15 @@
         <v>75</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
     </row>
-    <row r="128" hidden="true">
+    <row r="128">
       <c r="A128" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16500,13 +16527,13 @@
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G128" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>75</v>
@@ -16515,17 +16542,17 @@
         <v>85</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>75</v>
@@ -16574,7 +16601,7 @@
         <v>75</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>76</v>
@@ -16595,15 +16622,15 @@
         <v>75</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16626,19 +16653,17 @@
         <v>85</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>255</v>
+        <v>98</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>75</v>
@@ -16687,7 +16712,7 @@
         <v>75</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>76</v>
@@ -16708,15 +16733,15 @@
         <v>75</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16739,19 +16764,19 @@
         <v>85</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>98</v>
+        <v>255</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>352</v>
+        <v>256</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>353</v>
+        <v>257</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>354</v>
+        <v>258</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>355</v>
+        <v>259</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>75</v>
@@ -16800,7 +16825,7 @@
         <v>75</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>356</v>
+        <v>260</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>76</v>
@@ -16821,15 +16846,15 @@
         <v>75</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>357</v>
+        <v>261</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16852,18 +16877,20 @@
         <v>85</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>308</v>
+        <v>98</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>595</v>
+        <v>352</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>596</v>
+        <v>353</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="O131" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="O131" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P131" t="s" s="2">
         <v>75</v>
       </c>
@@ -16887,13 +16914,13 @@
         <v>75</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>598</v>
+        <v>75</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>599</v>
+        <v>75</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>75</v>
@@ -16911,7 +16938,7 @@
         <v>75</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>594</v>
+        <v>356</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
@@ -16932,7 +16959,7 @@
         <v>75</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>75</v>
+        <v>357</v>
       </c>
     </row>
     <row r="132" hidden="true">
@@ -16951,7 +16978,7 @@
         <v>76</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>75</v>
@@ -16960,19 +16987,19 @@
         <v>75</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K132" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L132" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="L132" t="s" s="2">
+      <c r="M132" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -16998,13 +17025,13 @@
         <v>75</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>75</v>
+        <v>604</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>75</v>
+        <v>605</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>75</v>
@@ -17028,7 +17055,7 @@
         <v>76</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>75</v>
@@ -17048,10 +17075,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17074,16 +17101,16 @@
         <v>75</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>308</v>
+        <v>607</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -17109,13 +17136,13 @@
         <v>75</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>609</v>
+        <v>75</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>610</v>
+        <v>75</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>75</v>
@@ -17133,7 +17160,7 @@
         <v>75</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>76</v>
@@ -17185,18 +17212,18 @@
         <v>75</v>
       </c>
       <c r="K134" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L134" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="L134" t="s" s="2">
+      <c r="M134" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="N134" s="2"/>
-      <c r="O134" t="s" s="2">
-        <v>615</v>
-      </c>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>75</v>
       </c>
@@ -17220,13 +17247,13 @@
         <v>75</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>75</v>
+        <v>615</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>75</v>
+        <v>616</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>75</v>
@@ -17270,10 +17297,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17296,16 +17323,18 @@
         <v>75</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>308</v>
+        <v>618</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N135" s="2"/>
-      <c r="O135" s="2"/>
+      <c r="O135" t="s" s="2">
+        <v>621</v>
+      </c>
       <c r="P135" t="s" s="2">
         <v>75</v>
       </c>
@@ -17329,13 +17358,13 @@
         <v>75</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>619</v>
+        <v>75</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>620</v>
+        <v>75</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>75</v>
@@ -17353,7 +17382,7 @@
         <v>75</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>76</v>
@@ -17377,12 +17406,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17396,7 +17425,7 @@
         <v>77</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>75</v>
@@ -17405,7 +17434,7 @@
         <v>75</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>622</v>
+        <v>308</v>
       </c>
       <c r="L136" t="s" s="2">
         <v>623</v>
@@ -17438,13 +17467,13 @@
         <v>75</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>75</v>
+        <v>625</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>75</v>
+        <v>626</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>75</v>
@@ -17462,7 +17491,7 @@
         <v>75</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>76</v>
@@ -17477,16 +17506,16 @@
         <v>96</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>625</v>
+        <v>75</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>626</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="137" hidden="true">
+    <row r="137">
       <c r="A137" t="s" s="2">
         <v>627</v>
       </c>
@@ -17505,7 +17534,7 @@
         <v>77</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>75</v>
@@ -17514,13 +17543,13 @@
         <v>75</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>514</v>
+        <v>628</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -17586,21 +17615,21 @@
         <v>96</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>75</v>
+        <v>631</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>75</v>
+        <v>632</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17611,7 +17640,7 @@
         <v>76</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>75</v>
@@ -17623,13 +17652,13 @@
         <v>75</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>98</v>
+        <v>515</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>99</v>
+        <v>634</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>100</v>
+        <v>635</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -17680,19 +17709,19 @@
         <v>75</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>101</v>
+        <v>633</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>75</v>
@@ -17706,21 +17735,21 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>75</v>
@@ -17732,17 +17761,15 @@
         <v>75</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N139" s="2"/>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>75</v>
@@ -17791,19 +17818,19 @@
         <v>75</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>75</v>
@@ -17817,14 +17844,14 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>521</v>
+        <v>103</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -17837,26 +17864,24 @@
         <v>75</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K140" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>522</v>
+        <v>105</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>523</v>
+        <v>106</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="O140" t="s" s="2">
-        <v>265</v>
-      </c>
+      <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>75</v>
       </c>
@@ -17904,7 +17929,7 @@
         <v>75</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>524</v>
+        <v>111</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>76</v>
@@ -17930,42 +17955,46 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>75</v>
+        <v>522</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I141" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>308</v>
+        <v>104</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>634</v>
+        <v>523</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="N141" s="2"/>
-      <c r="O141" s="2"/>
+        <v>524</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P141" t="s" s="2">
         <v>75</v>
       </c>
@@ -17989,13 +18018,13 @@
         <v>75</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>163</v>
+        <v>75</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>636</v>
+        <v>75</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>637</v>
+        <v>75</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>75</v>
@@ -18013,19 +18042,19 @@
         <v>75</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>633</v>
+        <v>525</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>75</v>
@@ -18039,10 +18068,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18050,7 +18079,7 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G142" t="s" s="2">
         <v>84</v>
@@ -18065,7 +18094,7 @@
         <v>75</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>639</v>
+        <v>308</v>
       </c>
       <c r="L142" t="s" s="2">
         <v>640</v>
@@ -18098,13 +18127,13 @@
         <v>75</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>75</v>
+        <v>642</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>75</v>
+        <v>643</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>75</v>
@@ -18122,10 +18151,10 @@
         <v>75</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>84</v>
@@ -18148,10 +18177,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18159,10 +18188,10 @@
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>75</v>
@@ -18174,20 +18203,16 @@
         <v>75</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="O143" t="s" s="2">
         <v>647</v>
       </c>
+      <c r="N143" s="2"/>
+      <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>75</v>
       </c>
@@ -18235,13 +18260,13 @@
         <v>75</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>75</v>
@@ -18287,18 +18312,20 @@
         <v>75</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>308</v>
+        <v>649</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="O144" s="2"/>
+        <v>652</v>
+      </c>
+      <c r="O144" t="s" s="2">
+        <v>653</v>
+      </c>
       <c r="P144" t="s" s="2">
         <v>75</v>
       </c>
@@ -18322,13 +18349,13 @@
         <v>75</v>
       </c>
       <c r="X144" t="s" s="2">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="Y144" t="s" s="2">
-        <v>651</v>
+        <v>75</v>
       </c>
       <c r="Z144" t="s" s="2">
-        <v>652</v>
+        <v>75</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>75</v>
@@ -18370,8 +18397,119 @@
         <v>75</v>
       </c>
     </row>
+    <row r="145" hidden="true">
+      <c r="A145" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E145" s="2"/>
+      <c r="F145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H145" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I145" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J145" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K145" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="O145" s="2"/>
+      <c r="P145" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q145" s="2"/>
+      <c r="R145" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S145" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T145" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U145" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V145" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W145" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X145" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF145" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI145" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ145" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK145" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL145" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AM144">
+  <autoFilter ref="A1:AM145">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18381,7 +18519,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI143">
+  <conditionalFormatting sqref="A2:AI144">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
